--- a/Lane-Change/test/Results_Mix_test_Attacker_V1.xlsx
+++ b/Lane-Change/test/Results_Mix_test_Attacker_V1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="1271">
   <si>
     <t>AttackType</t>
   </si>
@@ -3539,6 +3539,294 @@
   </si>
   <si>
     <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 4</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 4</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 4</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 4</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 5</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 5</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 5</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 5</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 6</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 6</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 6</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 6</t>
+  </si>
+  <si>
+    <t>V5</t>
   </si>
 </sst>
 </file>
@@ -3584,7 +3872,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K292"/>
+  <dimension ref="A1:K316"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.26953125" customWidth="true"/>
@@ -12074,6 +12362,846 @@
       <c r="J292" s="0"/>
       <c r="K292" s="0"/>
     </row>
+    <row r="293">
+      <c r="A293" s="0" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B293" s="0" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C293" s="0" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D293" s="0" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E293" s="0">
+        <v>0.10732426425221686</v>
+      </c>
+      <c r="F293" s="0">
+        <v>0.018273910062149575</v>
+      </c>
+      <c r="G293" s="0">
+        <v>0.031108214984385936</v>
+      </c>
+      <c r="H293" s="0">
+        <v>0.0041393639824678953</v>
+      </c>
+      <c r="I293" s="0">
+        <v>0.36717039376949456</v>
+      </c>
+      <c r="J293" s="0">
+        <v>0.40791822468683198</v>
+      </c>
+      <c r="K293" s="0">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B294" s="0" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C294" s="0" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D294" s="0" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E294" s="0">
+        <v>0.11074962891786877</v>
+      </c>
+      <c r="F294" s="0">
+        <v>0.016776267163890118</v>
+      </c>
+      <c r="G294" s="0">
+        <v>0.028252379584368829</v>
+      </c>
+      <c r="H294" s="0">
+        <v>0.0047908081247073917</v>
+      </c>
+      <c r="I294" s="0">
+        <v>0.23075662304753192</v>
+      </c>
+      <c r="J294" s="0">
+        <v>0.24727974532763183</v>
+      </c>
+      <c r="K294" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B295" s="0" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C295" s="0" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D295" s="0" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E295" s="0">
+        <v>0.11933031939807145</v>
+      </c>
+      <c r="F295" s="0">
+        <v>0.017784175958488656</v>
+      </c>
+      <c r="G295" s="0">
+        <v>0.029212587816441218</v>
+      </c>
+      <c r="H295" s="0">
+        <v>0.008395812828653702</v>
+      </c>
+      <c r="I295" s="0">
+        <v>0.21273001201485048</v>
+      </c>
+      <c r="J295" s="0">
+        <v>0.21014929787592304</v>
+      </c>
+      <c r="K295" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B296" s="0" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C296" s="0" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D296" s="0" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E296" s="0">
+        <v>0.11483001224380446</v>
+      </c>
+      <c r="F296" s="0">
+        <v>0.017069264836288366</v>
+      </c>
+      <c r="G296" s="0">
+        <v>0.031671599502346465</v>
+      </c>
+      <c r="H296" s="0">
+        <v>0.012946153296916058</v>
+      </c>
+      <c r="I296" s="0">
+        <v>0.16807253110440917</v>
+      </c>
+      <c r="J296" s="0">
+        <v>0.18589688600394685</v>
+      </c>
+      <c r="K296" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="0" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B297" s="0" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C297" s="0" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D297" s="0" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E297" s="0">
+        <v>0.11803093111448476</v>
+      </c>
+      <c r="F297" s="0">
+        <v>0.018606802201514679</v>
+      </c>
+      <c r="G297" s="0">
+        <v>0.029096764454307346</v>
+      </c>
+      <c r="H297" s="0">
+        <v>0.0040660673489866916</v>
+      </c>
+      <c r="I297" s="0">
+        <v>0.4640225503027563</v>
+      </c>
+      <c r="J297" s="0">
+        <v>0.065246336470038413</v>
+      </c>
+      <c r="K297" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B298" s="0" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C298" s="0" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D298" s="0" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E298" s="0">
+        <v>0.11654438629176563</v>
+      </c>
+      <c r="F298" s="0">
+        <v>0.01663865662791358</v>
+      </c>
+      <c r="G298" s="0">
+        <v>0.029872514941801424</v>
+      </c>
+      <c r="H298" s="0">
+        <v>0.0050781159861256779</v>
+      </c>
+      <c r="I298" s="0">
+        <v>0.31649168408140677</v>
+      </c>
+      <c r="J298" s="0">
+        <v>-0.018041049230582834</v>
+      </c>
+      <c r="K298" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B299" s="0" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C299" s="0" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D299" s="0" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E299" s="0">
+        <v>0.1098730577552558</v>
+      </c>
+      <c r="F299" s="0">
+        <v>0.018890645102573843</v>
+      </c>
+      <c r="G299" s="0">
+        <v>0.030456852782276982</v>
+      </c>
+      <c r="H299" s="0">
+        <v>0.0093423963794651878</v>
+      </c>
+      <c r="I299" s="0">
+        <v>0.27993914014801746</v>
+      </c>
+      <c r="J299" s="0">
+        <v>-0.015749677658886657</v>
+      </c>
+      <c r="K299" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B300" s="0" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C300" s="0" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D300" s="0" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E300" s="0">
+        <v>0.11228428867572612</v>
+      </c>
+      <c r="F300" s="0">
+        <v>0.016818962782963423</v>
+      </c>
+      <c r="G300" s="0">
+        <v>0.028597428902463196</v>
+      </c>
+      <c r="H300" s="0">
+        <v>0.013195734625437924</v>
+      </c>
+      <c r="I300" s="0">
+        <v>0.23379289431589337</v>
+      </c>
+      <c r="J300" s="0">
+        <v>0.0003601029804273792</v>
+      </c>
+      <c r="K300" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B301" s="0" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C301" s="0" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D301" s="0" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E301" s="0">
+        <v>0.12757409016648297</v>
+      </c>
+      <c r="F301" s="0">
+        <v>0.017661818542746885</v>
+      </c>
+      <c r="G301" s="0">
+        <v>0.03071823588057316</v>
+      </c>
+      <c r="H301" s="0">
+        <v>0.0042223363409324699</v>
+      </c>
+      <c r="I301" s="0">
+        <v>0.37209455253076656</v>
+      </c>
+      <c r="J301" s="0">
+        <v>0.42072617766750642</v>
+      </c>
+      <c r="K301" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B302" s="0" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C302" s="0" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D302" s="0" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E302" s="0">
+        <v>0.11592236487362922</v>
+      </c>
+      <c r="F302" s="0">
+        <v>0.01805713641471865</v>
+      </c>
+      <c r="G302" s="0">
+        <v>0.029324680736629211</v>
+      </c>
+      <c r="H302" s="0">
+        <v>0.0052128332505918685</v>
+      </c>
+      <c r="I302" s="0">
+        <v>0.23274954686226479</v>
+      </c>
+      <c r="J302" s="0">
+        <v>0.25795519386109628</v>
+      </c>
+      <c r="K302" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="0" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B303" s="0" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C303" s="0" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D303" s="0" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E303" s="0">
+        <v>0.12025087422366981</v>
+      </c>
+      <c r="F303" s="0">
+        <v>0.017632724493766398</v>
+      </c>
+      <c r="G303" s="0">
+        <v>0.02758286603947455</v>
+      </c>
+      <c r="H303" s="0">
+        <v>0.0088549464125016377</v>
+      </c>
+      <c r="I303" s="0">
+        <v>0.21275001560750842</v>
+      </c>
+      <c r="J303" s="0">
+        <v>0.23991946332871947</v>
+      </c>
+      <c r="K303" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B304" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C304" s="0" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D304" s="0" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E304" s="0">
+        <v>0.11214740512070093</v>
+      </c>
+      <c r="F304" s="0">
+        <v>0.017568696801562145</v>
+      </c>
+      <c r="G304" s="0">
+        <v>0.02906099888345447</v>
+      </c>
+      <c r="H304" s="0">
+        <v>0.01420397719734018</v>
+      </c>
+      <c r="I304" s="0">
+        <v>0.17305262652557227</v>
+      </c>
+      <c r="J304" s="0">
+        <v>0.20713164377470134</v>
+      </c>
+      <c r="K304" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="0" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B305" s="0" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C305" s="0" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D305" s="0" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E305" s="0">
+        <v>0.10578309104685837</v>
+      </c>
+      <c r="F305" s="0">
+        <v>0.016943401849935265</v>
+      </c>
+      <c r="G305" s="0">
+        <v>0.031627604105917445</v>
+      </c>
+      <c r="H305" s="0">
+        <v>0.0039597559954548337</v>
+      </c>
+      <c r="I305" s="0">
+        <v>0.47739788220230595</v>
+      </c>
+      <c r="J305" s="0">
+        <v>0.023011635747786141</v>
+      </c>
+      <c r="K305" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="0" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B306" s="0" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C306" s="0" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D306" s="0" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E306" s="0">
+        <v>0.12170059992823022</v>
+      </c>
+      <c r="F306" s="0">
+        <v>0.017922432400424106</v>
+      </c>
+      <c r="G306" s="0">
+        <v>0.031172929171250335</v>
+      </c>
+      <c r="H306" s="0">
+        <v>0.0051107018498509158</v>
+      </c>
+      <c r="I306" s="0">
+        <v>0.31508801075115889</v>
+      </c>
+      <c r="J306" s="0">
+        <v>0.028339125752426253</v>
+      </c>
+      <c r="K306" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="0" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B307" s="0" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C307" s="0" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D307" s="0" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E307" s="0">
+        <v>0.12683674195774602</v>
+      </c>
+      <c r="F307" s="0">
+        <v>0.0184318294266686</v>
+      </c>
+      <c r="G307" s="0">
+        <v>0.031000450641660363</v>
+      </c>
+      <c r="H307" s="0">
+        <v>0.0091238474387783722</v>
+      </c>
+      <c r="I307" s="0">
+        <v>0.28835635568682644</v>
+      </c>
+      <c r="J307" s="0">
+        <v>0.056908287595233781</v>
+      </c>
+      <c r="K307" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="0" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B308" s="0" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C308" s="0" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D308" s="0" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E308" s="0">
+        <v>0.1173735780373388</v>
+      </c>
+      <c r="F308" s="0">
+        <v>0.017743077523733542</v>
+      </c>
+      <c r="G308" s="0">
+        <v>0.030647305757503206</v>
+      </c>
+      <c r="H308" s="0">
+        <v>0.014229998905510367</v>
+      </c>
+      <c r="I308" s="0">
+        <v>0.22979228600855978</v>
+      </c>
+      <c r="J308" s="0">
+        <v>0.068098935588492504</v>
+      </c>
+      <c r="K308" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="0" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B309" s="0" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C309" s="0" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D309" s="0" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E309" s="0">
+        <v>0.11311464165790443</v>
+      </c>
+      <c r="F309" s="0">
+        <v>0.018172967736050767</v>
+      </c>
+      <c r="G309" s="0">
+        <v>0.029230401969631538</v>
+      </c>
+      <c r="H309" s="0">
+        <v>0.0048394436752765575</v>
+      </c>
+      <c r="I309" s="0">
+        <v>0.47461449900248792</v>
+      </c>
+      <c r="J309" s="0">
+        <v>0.067961082085029323</v>
+      </c>
+      <c r="K309" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="0" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B310" s="0" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C310" s="0" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D310" s="0" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E310" s="0">
+        <v>0.10766040592880448</v>
+      </c>
+      <c r="F310" s="0">
+        <v>0.016621765452561894</v>
+      </c>
+      <c r="G310" s="0">
+        <v>0.029061422266490902</v>
+      </c>
+      <c r="H310" s="0">
+        <v>0.0053398600131811906</v>
+      </c>
+      <c r="I310" s="0">
+        <v>0.32549125705866555</v>
+      </c>
+      <c r="J310" s="0">
+        <v>-0.034272663366376521</v>
+      </c>
+      <c r="K310" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="0" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B311" s="0" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C311" s="0" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D311" s="0" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E311" s="0">
+        <v>0.13246219815246976</v>
+      </c>
+      <c r="F311" s="0">
+        <v>0.015977340128322831</v>
+      </c>
+      <c r="G311" s="0">
+        <v>0.031560005921708142</v>
+      </c>
+      <c r="H311" s="0">
+        <v>0.0093111521362520336</v>
+      </c>
+      <c r="I311" s="0">
+        <v>0.28981969373627686</v>
+      </c>
+      <c r="J311" s="0">
+        <v>-0.077508701584940887</v>
+      </c>
+      <c r="K311" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="0" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B312" s="0" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C312" s="0" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D312" s="0" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E312" s="0">
+        <v>0.11907172582339179</v>
+      </c>
+      <c r="F312" s="0">
+        <v>0.020161688996937422</v>
+      </c>
+      <c r="G312" s="0">
+        <v>0.030865092734604367</v>
+      </c>
+      <c r="H312" s="0">
+        <v>0.014547847575408888</v>
+      </c>
+      <c r="I312" s="0">
+        <v>0.23632620990425038</v>
+      </c>
+      <c r="J312" s="0">
+        <v>-0.0032925408439085091</v>
+      </c>
+      <c r="K312" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="0" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B313" s="0" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C313" s="0" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D313" s="0" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E313" s="0">
+        <v>0.11788850755528253</v>
+      </c>
+      <c r="F313" s="0">
+        <v>0.018162568858832509</v>
+      </c>
+      <c r="G313" s="0">
+        <v>0.028631857827431533</v>
+      </c>
+      <c r="H313" s="0">
+        <v>0.0043082976538529501</v>
+      </c>
+      <c r="I313" s="0">
+        <v>0.50574785075545581</v>
+      </c>
+      <c r="J313" s="0">
+        <v>-0.044421541447183854</v>
+      </c>
+      <c r="K313" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="0" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B314" s="0" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C314" s="0" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D314" s="0" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E314" s="0">
+        <v>0.10986133185036286</v>
+      </c>
+      <c r="F314" s="0">
+        <v>0.017133621468599824</v>
+      </c>
+      <c r="G314" s="0">
+        <v>0.02747848013531928</v>
+      </c>
+      <c r="H314" s="0">
+        <v>0.0053686753392088414</v>
+      </c>
+      <c r="I314" s="0">
+        <v>0.34214929554256285</v>
+      </c>
+      <c r="J314" s="0">
+        <v>-0.0851236497243677</v>
+      </c>
+      <c r="K314" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="0" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B315" s="0" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C315" s="0" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D315" s="0" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E315" s="0">
+        <v>0.10937145514453242</v>
+      </c>
+      <c r="F315" s="0">
+        <v>0.017727840559938146</v>
+      </c>
+      <c r="G315" s="0">
+        <v>0.028606652426469582</v>
+      </c>
+      <c r="H315" s="0">
+        <v>0.010008670172699985</v>
+      </c>
+      <c r="I315" s="0">
+        <v>0.32961890834033053</v>
+      </c>
+      <c r="J315" s="0">
+        <v>-0.070782729152719159</v>
+      </c>
+      <c r="K315" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="0" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B316" s="0" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C316" s="0" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D316" s="0" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E316" s="0">
+        <v>0.12431461118878989</v>
+      </c>
+      <c r="F316" s="0">
+        <v>0.017999146673619161</v>
+      </c>
+      <c r="G316" s="0">
+        <v>0.030337814159498509</v>
+      </c>
+      <c r="H316" s="0">
+        <v>0.014468247426438199</v>
+      </c>
+      <c r="I316" s="0">
+        <v>0.27617847092582204</v>
+      </c>
+      <c r="J316" s="0">
+        <v>-0.081533050043957528</v>
+      </c>
+      <c r="K316" s="0">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>